--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:17:51+00:00</t>
+    <t>2023-02-15T16:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:22:21+00:00</t>
+    <t>2023-02-15T20:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T20:04:03+00:00</t>
+    <t>2023-02-16T23:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6593,7 +6593,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>336</v>
       </c>
@@ -6609,7 +6609,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>72</v>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-16T23:28:10+00:00</t>
+    <t>2023-02-17T19:45:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-17T19:45:07+00:00</t>
+    <t>2023-02-20T03:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3663,7 +3663,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>188</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>72</v>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>80</v>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$51</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="362">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -641,131 +641,10 @@
     <t>eventCoding</t>
   </si>
   <si>
-    <t>MessageHeader.event[x].id</t>
-  </si>
-  <si>
-    <t>MessageHeader.event[x].extension</t>
-  </si>
-  <si>
-    <t>MessageHeader.event[x].system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>MessageHeader.event[x].version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>MessageHeader.event[x].code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
     <t>required</t>
   </si>
   <si>
     <t>http://minsal.cl/listaespera/ValueSet/VSTipoEventoLE</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>MessageHeader.event[x].display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>MessageHeader.event[x].userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
   </si>
   <si>
     <t>MessageHeader.destination</t>
@@ -1564,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL58"/>
+  <dimension ref="A1:AL51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.80859375" customWidth="true" bestFit="true"/>
@@ -3727,13 +3606,11 @@
         <v>72</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="X20" s="2"/>
       <c r="Y20" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>72</v>
@@ -3777,7 +3654,7 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -3788,7 +3665,7 @@
         <v>73</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>72</v>
@@ -3797,19 +3674,23 @@
         <v>72</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>204</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>94</v>
+        <v>205</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O21" t="s" s="2">
         <v>72</v>
       </c>
@@ -3857,44 +3738,44 @@
         <v>72</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>96</v>
+        <v>203</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>72</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>72</v>
@@ -3906,17 +3787,15 @@
         <v>72</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>103</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
         <v>72</v>
@@ -3953,31 +3832,31 @@
         <v>72</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="AC22" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>72</v>
@@ -3991,18 +3870,18 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>72</v>
@@ -4011,23 +3890,21 @@
         <v>72</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>205</v>
+        <v>102</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
         <v>72</v>
       </c>
@@ -4075,25 +3952,25 @@
         <v>72</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>208</v>
+        <v>107</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>209</v>
+        <v>72</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>210</v>
+        <v>97</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>72</v>
@@ -4101,41 +3978,43 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>72</v>
+        <v>214</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>72</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="O24" t="s" s="2">
         <v>72</v>
       </c>
@@ -4183,25 +4062,25 @@
         <v>72</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>216</v>
+        <v>72</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>217</v>
+        <v>179</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>72</v>
@@ -4232,7 +4111,7 @@
         <v>81</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>219</v>
@@ -4267,11 +4146,13 @@
         <v>72</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="X25" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Y25" t="s" s="2">
-        <v>223</v>
+        <v>72</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>72</v>
@@ -4289,7 +4170,7 @@
         <v>72</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>73</v>
@@ -4304,10 +4185,10 @@
         <v>114</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>72</v>
@@ -4315,7 +4196,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4338,17 +4219,17 @@
         <v>81</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="O26" t="s" s="2">
         <v>72</v>
@@ -4397,7 +4278,7 @@
         <v>72</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>73</v>
@@ -4412,10 +4293,10 @@
         <v>114</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>232</v>
+        <v>72</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>72</v>
@@ -4423,7 +4304,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4431,7 +4312,7 @@
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
@@ -4446,19 +4327,19 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O27" t="s" s="2">
         <v>72</v>
@@ -4507,10 +4388,10 @@
         <v>72</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4522,10 +4403,10 @@
         <v>114</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>72</v>
@@ -4533,7 +4414,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4544,7 +4425,7 @@
         <v>73</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>72</v>
@@ -4556,19 +4437,17 @@
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="M28" s="2"/>
       <c r="N28" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>72</v>
@@ -4617,13 +4496,13 @@
         <v>72</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>72</v>
@@ -4632,18 +4511,18 @@
         <v>114</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>72</v>
+        <v>243</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>250</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -4663,19 +4542,23 @@
         <v>72</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>93</v>
+        <v>239</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>94</v>
+        <v>246</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O29" t="s" s="2">
         <v>72</v>
       </c>
@@ -4723,7 +4606,7 @@
         <v>72</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>96</v>
+        <v>245</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>73</v>
@@ -4735,32 +4618,32 @@
         <v>72</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>72</v>
+        <v>243</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>97</v>
+        <v>244</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>72</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>72</v>
@@ -4769,21 +4652,23 @@
         <v>72</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>101</v>
+        <v>251</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>102</v>
+        <v>252</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="O30" t="s" s="2">
         <v>72</v>
       </c>
@@ -4831,68 +4716,68 @@
         <v>72</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>107</v>
+        <v>249</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>72</v>
+        <v>255</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>97</v>
+        <v>256</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>72</v>
+        <v>257</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>254</v>
+        <v>72</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>103</v>
+        <v>253</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="O31" t="s" s="2">
         <v>72</v>
@@ -4941,33 +4826,33 @@
         <v>72</v>
       </c>
       <c r="AE31" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>72</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -4975,7 +4860,7 @@
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4990,17 +4875,17 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>93</v>
+        <v>204</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="O32" t="s" s="2">
         <v>72</v>
@@ -5049,10 +4934,10 @@
         <v>72</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5061,21 +4946,21 @@
         <v>72</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>262</v>
+        <v>72</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>72</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -5095,21 +4980,19 @@
         <v>72</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>265</v>
+        <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>266</v>
+        <v>94</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>267</v>
+        <v>95</v>
       </c>
       <c r="M33" s="2"/>
-      <c r="N33" t="s" s="2">
-        <v>268</v>
-      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
         <v>72</v>
       </c>
@@ -5157,7 +5040,7 @@
         <v>72</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>264</v>
+        <v>96</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>73</v>
@@ -5169,13 +5052,13 @@
         <v>72</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>269</v>
+        <v>97</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>72</v>
@@ -5183,18 +5066,18 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>72</v>
@@ -5203,23 +5086,21 @@
         <v>72</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>272</v>
+        <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>273</v>
+        <v>102</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
         <v>72</v>
       </c>
@@ -5267,25 +5148,25 @@
         <v>72</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>270</v>
+        <v>107</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>276</v>
+        <v>72</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>277</v>
+        <v>97</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>72</v>
@@ -5293,40 +5174,42 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>72</v>
+        <v>214</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>72</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>279</v>
+        <v>100</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>280</v>
+        <v>215</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M35" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N35" t="s" s="2">
-        <v>282</v>
+        <v>186</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>72</v>
@@ -5375,33 +5258,33 @@
         <v>72</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>278</v>
+        <v>217</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>283</v>
+        <v>72</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>284</v>
+        <v>179</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>250</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5424,19 +5307,17 @@
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>279</v>
+        <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>286</v>
+        <v>219</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="M36" s="2"/>
       <c r="N36" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>72</v>
@@ -5485,7 +5366,7 @@
         <v>72</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>73</v>
@@ -5500,18 +5381,18 @@
         <v>114</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>250</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -5519,13 +5400,13 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>72</v>
@@ -5534,19 +5415,17 @@
         <v>81</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>290</v>
+        <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="M37" s="2"/>
       <c r="N37" t="s" s="2">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="O37" t="s" s="2">
         <v>72</v>
@@ -5595,7 +5474,7 @@
         <v>72</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>73</v>
@@ -5610,18 +5489,18 @@
         <v>114</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>297</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -5629,13 +5508,13 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>72</v>
@@ -5644,19 +5523,17 @@
         <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>299</v>
+        <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="M38" s="2"/>
       <c r="N38" t="s" s="2">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>72</v>
@@ -5705,7 +5582,7 @@
         <v>72</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>73</v>
@@ -5720,18 +5597,18 @@
         <v>114</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>297</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -5739,7 +5616,7 @@
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5754,17 +5631,17 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>244</v>
+        <v>290</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" t="s" s="2">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>72</v>
@@ -5813,10 +5690,10 @@
         <v>72</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5825,21 +5702,21 @@
         <v>72</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>72</v>
+        <v>294</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>309</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -5847,31 +5724,35 @@
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>93</v>
+        <v>231</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>94</v>
+        <v>297</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O40" t="s" s="2">
         <v>72</v>
       </c>
@@ -5919,10 +5800,10 @@
         <v>72</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>96</v>
+        <v>296</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5931,13 +5812,13 @@
         <v>72</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>72</v>
+        <v>300</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>97</v>
+        <v>301</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>72</v>
@@ -5945,18 +5826,18 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>72</v>
@@ -5965,21 +5846,23 @@
         <v>72</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>100</v>
+        <v>239</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>101</v>
+        <v>303</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="O41" t="s" s="2">
         <v>72</v>
       </c>
@@ -6027,68 +5910,66 @@
         <v>72</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>107</v>
+        <v>302</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>72</v>
+        <v>305</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>97</v>
+        <v>306</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>72</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
-        <v>254</v>
+        <v>72</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>72</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>100</v>
+        <v>309</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>103</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="M42" s="2"/>
       <c r="N42" t="s" s="2">
-        <v>186</v>
+        <v>312</v>
       </c>
       <c r="O42" t="s" s="2">
         <v>72</v>
@@ -6113,13 +5994,13 @@
         <v>72</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>72</v>
+        <v>146</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>72</v>
+        <v>313</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>72</v>
+        <v>314</v>
       </c>
       <c r="Z42" t="s" s="2">
         <v>72</v>
@@ -6137,33 +6018,33 @@
         <v>72</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>257</v>
+        <v>308</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>72</v>
+        <v>315</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>179</v>
+        <v>316</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>72</v>
+        <v>317</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6186,18 +6067,16 @@
         <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>93</v>
+        <v>204</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>259</v>
+        <v>319</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M43" s="2"/>
-      <c r="N43" t="s" s="2">
-        <v>315</v>
-      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
         <v>72</v>
       </c>
@@ -6245,7 +6124,7 @@
         <v>72</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>73</v>
@@ -6260,18 +6139,18 @@
         <v>114</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -6279,33 +6158,31 @@
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>319</v>
+        <v>94</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>320</v>
+        <v>95</v>
       </c>
       <c r="M44" s="2"/>
-      <c r="N44" t="s" s="2">
-        <v>321</v>
-      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
         <v>72</v>
       </c>
@@ -6353,7 +6230,7 @@
         <v>72</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>318</v>
+        <v>96</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>73</v>
@@ -6365,13 +6242,13 @@
         <v>72</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>322</v>
+        <v>72</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>323</v>
+        <v>97</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>72</v>
@@ -6383,14 +6260,14 @@
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>72</v>
@@ -6399,21 +6276,21 @@
         <v>72</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>325</v>
+        <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="M45" s="2"/>
-      <c r="N45" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
         <v>72</v>
       </c>
@@ -6461,25 +6338,25 @@
         <v>72</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>324</v>
+        <v>107</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>327</v>
+        <v>72</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>328</v>
+        <v>97</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>72</v>
@@ -6487,40 +6364,42 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
-        <v>72</v>
+        <v>214</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
         <v>73</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>72</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>330</v>
+        <v>100</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>331</v>
+        <v>215</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="M46" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N46" t="s" s="2">
-        <v>333</v>
+        <v>186</v>
       </c>
       <c r="O46" t="s" s="2">
         <v>72</v>
@@ -6569,33 +6448,33 @@
         <v>72</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>329</v>
+        <v>217</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>334</v>
+        <v>72</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>335</v>
+        <v>179</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -6609,7 +6488,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>72</v>
@@ -6618,19 +6497,17 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="M47" s="2"/>
       <c r="N47" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>72</v>
@@ -6679,7 +6556,7 @@
         <v>72</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>80</v>
@@ -6694,10 +6571,10 @@
         <v>114</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>72</v>
@@ -6705,7 +6582,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -6713,7 +6590,7 @@
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>80</v>
@@ -6728,19 +6605,19 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>279</v>
+        <v>156</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>293</v>
+        <v>335</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>294</v>
+        <v>336</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>72</v>
@@ -6765,13 +6642,13 @@
         <v>72</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>72</v>
+        <v>201</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>72</v>
+        <v>337</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>72</v>
+        <v>338</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>72</v>
@@ -6789,10 +6666,10 @@
         <v>72</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6804,18 +6681,18 @@
         <v>114</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>347</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -6838,17 +6715,19 @@
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M49" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="N49" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>72</v>
@@ -6873,13 +6752,13 @@
         <v>72</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>353</v>
+        <v>72</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>354</v>
+        <v>72</v>
       </c>
       <c r="Z49" t="s" s="2">
         <v>72</v>
@@ -6897,7 +6776,7 @@
         <v>72</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>73</v>
@@ -6912,18 +6791,18 @@
         <v>114</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>357</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
@@ -6931,13 +6810,13 @@
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>72</v>
@@ -6946,16 +6825,20 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>244</v>
+        <v>350</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O50" t="s" s="2">
         <v>72</v>
       </c>
@@ -7003,13 +6886,13 @@
         <v>72</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>72</v>
@@ -7018,10 +6901,10 @@
         <v>114</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>361</v>
+        <v>72</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>72</v>
@@ -7029,7 +6912,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7049,19 +6932,21 @@
         <v>72</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>357</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>94</v>
+        <v>358</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>95</v>
+        <v>359</v>
       </c>
       <c r="M51" s="2"/>
-      <c r="N51" s="2"/>
+      <c r="N51" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O51" t="s" s="2">
         <v>72</v>
       </c>
@@ -7109,7 +6994,7 @@
         <v>72</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>96</v>
+        <v>356</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>73</v>
@@ -7121,784 +7006,20 @@
         <v>72</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>97</v>
+        <v>361</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="B52" s="2"/>
-      <c r="C52" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="D52" s="2"/>
-      <c r="E52" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="F52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="P52" s="2"/>
-      <c r="Q52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="R52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="B53" s="2"/>
-      <c r="C53" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="D53" s="2"/>
-      <c r="E53" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="F53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="P53" s="2"/>
-      <c r="Q53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="R53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="B54" s="2"/>
-      <c r="C54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="D54" s="2"/>
-      <c r="E54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="F54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="M54" s="2"/>
-      <c r="N54" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="P54" s="2"/>
-      <c r="Q54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="R54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B55" s="2"/>
-      <c r="C55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="D55" s="2"/>
-      <c r="E55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="F55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="P55" s="2"/>
-      <c r="Q55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="R55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="B56" s="2"/>
-      <c r="C56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="D56" s="2"/>
-      <c r="E56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="F56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="P56" s="2"/>
-      <c r="Q56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="R56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="B57" s="2"/>
-      <c r="C57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="D57" s="2"/>
-      <c r="E57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="F57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="P57" s="2"/>
-      <c r="Q57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="R57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="B58" s="2"/>
-      <c r="C58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="D58" s="2"/>
-      <c r="E58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="F58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="M58" s="2"/>
-      <c r="N58" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="P58" s="2"/>
-      <c r="Q58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="R58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AL58" t="s" s="2">
         <v>72</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL58">
+  <autoFilter ref="A1:AL51">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7908,7 +7029,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI57">
+  <conditionalFormatting sqref="A2:AI50">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-MessageHeaderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
